--- a/E/SWAEGB.xlsx
+++ b/E/SWAEGB.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
   <si>
     <t/>
   </si>
@@ -50,6 +50,81 @@
   </si>
   <si>
     <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20115354</t>
+  </si>
+  <si>
+    <t>DNCOW FRTG CKL 4X110</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>20128794</t>
+  </si>
+  <si>
+    <t>NS/GOODNES KURMA 189</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20139359</t>
+  </si>
+  <si>
+    <t>KIT KAT CHO KLG 220</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20135340</t>
+  </si>
+  <si>
+    <t>MILO DRNK EXT.CHO220</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20136451</t>
+  </si>
+  <si>
+    <t>NSCAFE AMERICANO 10S</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
 </sst>
 </file>
@@ -442,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -532,6 +607,186 @@
         <v>12</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/SWAEGB.xlsx
+++ b/E/SWAEGB.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
   <si>
     <t/>
   </si>
@@ -517,17 +517,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,8 +547,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -563,11 +570,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -583,11 +590,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -603,11 +610,11 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -623,11 +630,11 @@
       <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -643,11 +650,11 @@
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -663,11 +670,11 @@
       <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -683,11 +690,11 @@
       <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -703,11 +710,11 @@
       <c r="E9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -723,11 +730,11 @@
       <c r="E10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -743,11 +750,11 @@
       <c r="E11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -763,11 +770,11 @@
       <c r="E12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -783,7 +790,7 @@
       <c r="E13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/SWAEGB.xlsx
+++ b/E/SWAEGB.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
   <si>
     <t/>
   </si>
@@ -43,7 +43,7 @@
     <t>20137792</t>
   </si>
   <si>
-    <t>MAMA LIME GREEN 690</t>
+    <t>MAMA LIME GREEN 610</t>
   </si>
   <si>
     <t>3</t>
@@ -517,18 +517,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,14 +546,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -570,11 +563,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -590,11 +583,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -610,11 +603,11 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -630,11 +623,11 @@
       <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -650,11 +643,11 @@
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -670,11 +663,11 @@
       <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -690,11 +683,11 @@
       <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
@@ -710,11 +703,11 @@
       <c r="E9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>25</v>
       </c>
@@ -730,11 +723,11 @@
       <c r="E10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>28</v>
       </c>
@@ -750,11 +743,11 @@
       <c r="E11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -770,11 +763,11 @@
       <c r="E12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -790,7 +783,7 @@
       <c r="E13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/SWAEGB.xlsx
+++ b/E/SWAEGB.xlsx
@@ -16,115 +16,115 @@
     <t/>
   </si>
   <si>
+    <t>20115354</t>
+  </si>
+  <si>
+    <t>DNCOW FRTG CKL 4X110</t>
+  </si>
+  <si>
+    <t>SWAEGB</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20128794</t>
+  </si>
+  <si>
+    <t>NS/GOODNES KURMA 189</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20139359</t>
+  </si>
+  <si>
+    <t>KIT KAT CHO KLG 220</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20135340</t>
+  </si>
+  <si>
+    <t>MILO DRNK EXT.CHO220</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20136451</t>
+  </si>
+  <si>
+    <t>NSCAFE AMERICANO 10S</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>20133213</t>
   </si>
   <si>
     <t>BOOM DET.CAIR LAV510</t>
   </si>
   <si>
-    <t>SWAEGB</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20131792</t>
   </si>
   <si>
     <t>BOOM DET.BBK LVND770</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>20137792</t>
   </si>
   <si>
     <t>MAMA LIME GREEN 610</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20115354</t>
-  </si>
-  <si>
-    <t>DNCOW FRTG CKL 4X110</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CLGEN 189</t>
-  </si>
-  <si>
-    <t>20128794</t>
-  </si>
-  <si>
-    <t>NS/GOODNES KURMA 189</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20139359</t>
-  </si>
-  <si>
-    <t>KIT KAT CHO KLG 220</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20135340</t>
-  </si>
-  <si>
-    <t>MILO DRNK EXT.CHO220</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NESCAFE LATTE 220ML</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NESCAFE CPUCCINO 220</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20136451</t>
-  </si>
-  <si>
-    <t>NSCAFE AMERICANO 10S</t>
-  </si>
-  <si>
-    <t>9</t>
   </si>
 </sst>
 </file>
@@ -604,24 +604,24 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -641,7 +641,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -649,10 +649,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -661,7 +661,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -669,10 +669,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -681,18 +681,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -701,18 +701,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -721,7 +721,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -729,10 +729,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -741,18 +741,18 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -761,10 +761,10 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -781,10 +781,10 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/SWAEGB.xlsx
+++ b/E/SWAEGB.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="31">
   <si>
     <t/>
   </si>
@@ -104,27 +104,6 @@
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>20133213</t>
-  </si>
-  <si>
-    <t>BOOM DET.CAIR LAV510</t>
-  </si>
-  <si>
-    <t>20131792</t>
-  </si>
-  <si>
-    <t>BOOM DET.BBK LVND770</t>
-  </si>
-  <si>
-    <t>20137792</t>
-  </si>
-  <si>
-    <t>MAMA LIME GREEN 610</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
   </si>
 </sst>
 </file>
@@ -517,14 +496,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -727,66 +706,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
